--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:14:45+00:00</t>
+    <t>2023-03-24T14:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:42:38+00:00</t>
+    <t>2023-03-24T15:38:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T15:38:14+00:00</t>
+    <t>2023-03-26T08:37:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2238" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2238" uniqueCount="485">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T08:37:00+00:00</t>
+    <t>2023-03-26T09:07:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -773,6 +773,9 @@
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
   </si>
   <si>
+    <t>Patient internal identifier</t>
+  </si>
+  <si>
     <t>Coding.display</t>
   </si>
   <si>
@@ -829,6 +832,9 @@
   </si>
   <si>
     <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>HIV positive testing identifier</t>
   </si>
   <si>
     <t>CodeableConcept.text</t>
@@ -4804,7 +4810,7 @@
         <v>79</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>79</v>
+        <v>246</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>79</v>
@@ -4843,7 +4849,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4864,10 +4870,10 @@
         <v>79</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>79</v>
@@ -4878,10 +4884,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4904,19 +4910,19 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -4965,7 +4971,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4986,10 +4992,10 @@
         <v>79</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -5000,10 +5006,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5029,16 +5035,16 @@
         <v>162</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>79</v>
@@ -5048,7 +5054,7 @@
         <v>79</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>79</v>
@@ -5087,7 +5093,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5108,10 +5114,10 @@
         <v>79</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>79</v>
@@ -5122,10 +5128,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5151,29 +5157,29 @@
         <v>104</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>79</v>
@@ -5209,7 +5215,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5230,10 +5236,10 @@
         <v>79</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>79</v>
@@ -5244,10 +5250,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5273,13 +5279,13 @@
         <v>162</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5293,7 +5299,7 @@
         <v>79</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>79</v>
@@ -5329,7 +5335,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5350,10 +5356,10 @@
         <v>79</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5364,10 +5370,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5390,13 +5396,13 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5447,7 +5453,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5468,10 +5474,10 @@
         <v>79</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5482,10 +5488,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5508,16 +5514,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5567,7 +5573,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5588,10 +5594,10 @@
         <v>79</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -5602,10 +5608,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5631,13 +5637,13 @@
         <v>187</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5666,10 +5672,10 @@
         <v>180</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>79</v>
@@ -5687,7 +5693,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5696,25 +5702,25 @@
         <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>79</v>
@@ -5722,10 +5728,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5751,13 +5757,13 @@
         <v>187</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5786,10 +5792,10 @@
         <v>180</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>79</v>
@@ -5807,7 +5813,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5816,36 +5822,36 @@
         <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5871,13 +5877,13 @@
         <v>187</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5906,28 +5912,28 @@
         <v>192</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5945,16 +5951,16 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>79</v>
@@ -5962,10 +5968,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5991,13 +5997,13 @@
         <v>187</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6026,28 +6032,28 @@
         <v>114</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6065,31 +6071,31 @@
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6111,14 +6117,14 @@
         <v>187</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>79</v>
@@ -6147,7 +6153,7 @@
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
@@ -6165,7 +6171,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6180,30 +6186,30 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6229,13 +6235,13 @@
         <v>187</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6261,13 +6267,13 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -6285,7 +6291,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6303,31 +6309,31 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6346,17 +6352,17 @@
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>79</v>
@@ -6405,7 +6411,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>90</v>
@@ -6420,19 +6426,19 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>79</v>
@@ -6440,10 +6446,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6466,16 +6472,16 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6525,7 +6531,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6540,19 +6546,19 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>79</v>
@@ -6560,10 +6566,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6586,16 +6592,16 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6645,7 +6651,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6660,19 +6666,19 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>79</v>
@@ -6680,10 +6686,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6706,16 +6712,16 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6765,7 +6771,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6774,7 +6780,7 @@
         <v>90</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>102</v>
@@ -6789,10 +6795,10 @@
         <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>79</v>
@@ -6800,10 +6806,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6826,13 +6832,13 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6883,7 +6889,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6904,13 +6910,13 @@
         <v>79</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>79</v>
@@ -6918,10 +6924,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6944,13 +6950,13 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7001,7 +7007,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7025,10 +7031,10 @@
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>79</v>
@@ -7036,10 +7042,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7062,13 +7068,13 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7119,7 +7125,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7140,13 +7146,13 @@
         <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -7154,10 +7160,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7180,13 +7186,13 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7237,7 +7243,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7249,7 +7255,7 @@
         <v>79</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>79</v>
@@ -7261,7 +7267,7 @@
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7272,10 +7278,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7390,10 +7396,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7510,14 +7516,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7539,10 +7545,10 @@
         <v>136</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>139</v>
@@ -7597,7 +7603,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7632,10 +7638,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7661,10 +7667,10 @@
         <v>187</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7691,13 +7697,13 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -7715,7 +7721,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7724,7 +7730,7 @@
         <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>102</v>
@@ -7733,13 +7739,13 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -7750,10 +7756,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7776,13 +7782,13 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7833,7 +7839,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7842,7 +7848,7 @@
         <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>102</v>
@@ -7857,7 +7863,7 @@
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7868,10 +7874,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7897,10 +7903,10 @@
         <v>187</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7927,13 +7933,13 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -7951,7 +7957,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7975,7 +7981,7 @@
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -7986,10 +7992,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8012,16 +8018,16 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8071,7 +8077,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8083,7 +8089,7 @@
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
@@ -8095,7 +8101,7 @@
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -8106,10 +8112,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8224,10 +8230,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8344,14 +8350,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8373,10 +8379,10 @@
         <v>136</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>139</v>
@@ -8431,7 +8437,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8466,10 +8472,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8495,10 +8501,10 @@
         <v>187</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8525,13 +8531,13 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8549,7 +8555,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8558,25 +8564,25 @@
         <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>79</v>
@@ -8584,10 +8590,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8610,13 +8616,13 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8667,7 +8673,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8676,7 +8682,7 @@
         <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>102</v>
@@ -8691,10 +8697,10 @@
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>79</v>
@@ -8702,10 +8708,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8728,13 +8734,13 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8785,7 +8791,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8800,16 +8806,16 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>

--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T09:07:12+00:00</t>
+    <t>2023-03-26T10:42:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2238" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2391" uniqueCount="489">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T10:42:59+00:00</t>
+    <t>2023-03-26T11:23:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1134,6 +1134,18 @@
   </si>
   <si>
     <t>246090004</t>
+  </si>
+  <si>
+    <t>Condition.code.id</t>
+  </si>
+  <si>
+    <t>Condition.code.extension</t>
+  </si>
+  <si>
+    <t>Condition.code.coding</t>
+  </si>
+  <si>
+    <t>Condition.code.text</t>
   </si>
   <si>
     <t>Condition.bodySite</t>
@@ -1824,7 +1836,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP58"/>
+  <dimension ref="A1:AP62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.78515625" customWidth="true" bestFit="true"/>
@@ -6220,7 +6232,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>79</v>
@@ -6229,20 +6241,18 @@
         <v>79</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>362</v>
+        <v>163</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>79</v>
@@ -6267,13 +6277,13 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>365</v>
+        <v>79</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>366</v>
+        <v>79</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>367</v>
+        <v>79</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>79</v>
@@ -6291,56 +6301,56 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>361</v>
+        <v>165</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>368</v>
+        <v>79</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>369</v>
+        <v>166</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>370</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>372</v>
+        <v>135</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>79</v>
@@ -6349,21 +6359,21 @@
         <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>373</v>
+        <v>136</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>374</v>
+        <v>137</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>79</v>
       </c>
@@ -6399,46 +6409,46 @@
         <v>79</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>79</v>
+        <v>170</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>79</v>
+        <v>172</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>371</v>
+        <v>173</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>377</v>
+        <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>379</v>
+        <v>166</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>380</v>
+        <v>79</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>79</v>
@@ -6446,10 +6456,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6457,10 +6467,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -6472,18 +6482,20 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>382</v>
+        <v>203</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>383</v>
+        <v>204</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>384</v>
+        <v>205</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
       </c>
@@ -6531,13 +6543,13 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>381</v>
+        <v>208</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
@@ -6546,19 +6558,19 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>386</v>
+        <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>387</v>
+        <v>209</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>388</v>
+        <v>210</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>389</v>
+        <v>79</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>79</v>
@@ -6566,10 +6578,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6592,18 +6604,20 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>391</v>
+        <v>162</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>392</v>
+        <v>262</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>393</v>
+        <v>263</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>79</v>
       </c>
@@ -6612,7 +6626,7 @@
         <v>79</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>79</v>
@@ -6651,7 +6665,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>390</v>
+        <v>267</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6666,19 +6680,19 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>396</v>
+        <v>268</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>397</v>
+        <v>269</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>398</v>
+        <v>79</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>79</v>
@@ -6686,10 +6700,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6700,7 +6714,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>79</v>
@@ -6709,19 +6723,19 @@
         <v>79</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>391</v>
+        <v>187</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>400</v>
+        <v>366</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>401</v>
+        <v>367</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>402</v>
+        <v>368</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6747,13 +6761,13 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>79</v>
+        <v>369</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>79</v>
+        <v>370</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6771,16 +6785,16 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>102</v>
@@ -6789,31 +6803,31 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>79</v>
+        <v>372</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>404</v>
+        <v>373</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>405</v>
+        <v>79</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>79</v>
+        <v>374</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>79</v>
+        <v>376</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6832,16 +6846,18 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>407</v>
+        <v>377</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>408</v>
+        <v>378</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>409</v>
+        <v>379</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>79</v>
       </c>
@@ -6889,10 +6905,10 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>90</v>
@@ -6904,19 +6920,19 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>410</v>
+        <v>382</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>411</v>
+        <v>383</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>412</v>
+        <v>384</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>79</v>
@@ -6924,10 +6940,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>413</v>
+        <v>385</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>413</v>
+        <v>385</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6935,7 +6951,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>90</v>
@@ -6950,15 +6966,17 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>414</v>
+        <v>386</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>415</v>
+        <v>387</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -7007,7 +7025,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>413</v>
+        <v>385</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7022,19 +7040,19 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>79</v>
+        <v>390</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>79</v>
+        <v>391</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>417</v>
+        <v>392</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>418</v>
+        <v>393</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>79</v>
@@ -7042,10 +7060,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7068,15 +7086,17 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>420</v>
+        <v>396</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7125,7 +7145,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7140,19 +7160,19 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>79</v>
+        <v>399</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>422</v>
+        <v>400</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>423</v>
+        <v>401</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>424</v>
+        <v>402</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>79</v>
@@ -7160,10 +7180,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>425</v>
+        <v>403</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>425</v>
+        <v>403</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7174,7 +7194,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>79</v>
@@ -7186,15 +7206,17 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>426</v>
+        <v>395</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>427</v>
+        <v>404</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>79</v>
@@ -7243,19 +7265,19 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>425</v>
+        <v>403</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>79</v>
+        <v>407</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>429</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>79</v>
@@ -7267,10 +7289,10 @@
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>430</v>
+        <v>408</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>79</v>
+        <v>409</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>79</v>
@@ -7278,10 +7300,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7289,7 +7311,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>90</v>
@@ -7301,16 +7323,16 @@
         <v>79</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>162</v>
+        <v>411</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>163</v>
+        <v>412</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>164</v>
+        <v>413</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7361,7 +7383,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>165</v>
+        <v>410</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7373,7 +7395,7 @@
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>79</v>
@@ -7382,13 +7404,13 @@
         <v>79</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>79</v>
+        <v>414</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>166</v>
+        <v>415</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>79</v>
+        <v>416</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>79</v>
@@ -7396,21 +7418,21 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
@@ -7419,20 +7441,18 @@
         <v>79</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>136</v>
+        <v>418</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>137</v>
+        <v>419</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7481,19 +7501,19 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>173</v>
+        <v>417</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>79</v>
@@ -7505,10 +7525,10 @@
         <v>79</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>166</v>
+        <v>421</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>79</v>
+        <v>422</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>79</v>
@@ -7516,46 +7536,42 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>434</v>
+        <v>79</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>136</v>
+        <v>418</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7603,19 +7619,19 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
@@ -7624,13 +7640,13 @@
         <v>79</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>133</v>
+        <v>427</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>79</v>
+        <v>428</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>79</v>
@@ -7638,10 +7654,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7652,7 +7668,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>79</v>
@@ -7664,13 +7680,13 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>187</v>
+        <v>430</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7697,13 +7713,13 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>365</v>
+        <v>79</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>441</v>
+        <v>79</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>442</v>
+        <v>79</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
@@ -7721,31 +7737,31 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>443</v>
+        <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>102</v>
+        <v>433</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>444</v>
+        <v>79</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>316</v>
+        <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>358</v>
+        <v>434</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>79</v>
@@ -7756,10 +7772,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7770,7 +7786,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
@@ -7782,13 +7798,13 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>446</v>
+        <v>162</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>447</v>
+        <v>163</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>448</v>
+        <v>164</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7839,19 +7855,19 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>445</v>
+        <v>165</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>443</v>
+        <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
@@ -7863,7 +7879,7 @@
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>449</v>
+        <v>166</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7874,21 +7890,21 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>79</v>
@@ -7900,15 +7916,17 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>187</v>
+        <v>136</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>451</v>
+        <v>137</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -7933,13 +7951,13 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>365</v>
+        <v>79</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>453</v>
+        <v>79</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>454</v>
+        <v>79</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -7957,19 +7975,19 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>450</v>
+        <v>173</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>79</v>
@@ -7981,7 +7999,7 @@
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>455</v>
+        <v>166</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -7992,14 +8010,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>79</v>
+        <v>438</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8012,24 +8030,26 @@
         <v>79</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>426</v>
+        <v>136</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
       </c>
@@ -8077,7 +8097,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8089,7 +8109,7 @@
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>460</v>
+        <v>141</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
@@ -8101,7 +8121,7 @@
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>461</v>
+        <v>133</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -8112,10 +8132,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>462</v>
+        <v>442</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>462</v>
+        <v>442</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8138,13 +8158,13 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>163</v>
+        <v>443</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>164</v>
+        <v>444</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8171,13 +8191,13 @@
         <v>79</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>79</v>
+        <v>369</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>79</v>
+        <v>445</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>79</v>
+        <v>446</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -8195,7 +8215,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>165</v>
+        <v>442</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8204,22 +8224,22 @@
         <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>79</v>
+        <v>447</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>79</v>
+        <v>448</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>79</v>
+        <v>316</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>166</v>
+        <v>358</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8230,14 +8250,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8256,17 +8276,15 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>136</v>
+        <v>450</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>137</v>
+        <v>451</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8315,7 +8333,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>173</v>
+        <v>449</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8324,10 +8342,10 @@
         <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>79</v>
+        <v>447</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>79</v>
@@ -8339,7 +8357,7 @@
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>166</v>
+        <v>453</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8350,46 +8368,42 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>434</v>
+        <v>79</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8413,13 +8427,13 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>79</v>
+        <v>369</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>79</v>
+        <v>457</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>79</v>
+        <v>458</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8437,19 +8451,19 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>79</v>
@@ -8461,7 +8475,7 @@
         <v>79</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>133</v>
+        <v>459</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>79</v>
@@ -8472,10 +8486,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8495,18 +8509,20 @@
         <v>79</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>187</v>
+        <v>430</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -8531,13 +8547,13 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>365</v>
+        <v>79</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>468</v>
+        <v>79</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>469</v>
+        <v>79</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8555,7 +8571,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8564,25 +8580,25 @@
         <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>470</v>
+        <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>464</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>471</v>
+        <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>335</v>
+        <v>79</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>473</v>
+        <v>79</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>79</v>
@@ -8590,10 +8606,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8604,7 +8620,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>79</v>
@@ -8613,16 +8629,16 @@
         <v>79</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>475</v>
+        <v>162</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>476</v>
+        <v>163</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>477</v>
+        <v>164</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8673,19 +8689,19 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>474</v>
+        <v>165</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>470</v>
+        <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
@@ -8697,10 +8713,10 @@
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>449</v>
+        <v>166</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>473</v>
+        <v>79</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>79</v>
@@ -8708,21 +8724,21 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>79</v>
@@ -8734,15 +8750,17 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>479</v>
+        <v>136</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>480</v>
+        <v>137</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -8791,7 +8809,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>478</v>
+        <v>173</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8803,24 +8821,500 @@
         <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK58" t="s" s="2">
+      <c r="AK60" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AL58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM58" t="s" s="2">
+      <c r="B62" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K62" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="L62" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="AO58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP58" t="s" s="2">
+      <c r="M62" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:23:31+00:00</t>
+    <t>2023-03-27T11:26:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>90</v>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>90</v>
@@ -9216,7 +9216,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>79</v>

--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T11:26:57+00:00</t>
+    <t>2023-03-27T12:10:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T12:10:50+00:00</t>
+    <t>2023-03-28T07:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-28T07:53:05+00:00</t>
+    <t>2023-03-29T11:10:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-29T11:10:06+00:00</t>
+    <t>2023-04-03T05:56:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T05:56:04+00:00</t>
+    <t>2023-04-03T09:57:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$62</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T09:57:00+00:00</t>
+    <t>2023-04-03T10:41:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1663,6 +1666,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -2010,7 +2028,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2128,7 +2146,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>89</v>
       </c>
@@ -2248,7 +2266,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>97</v>
       </c>
@@ -2366,7 +2384,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>103</v>
       </c>
@@ -2486,7 +2504,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>109</v>
       </c>
@@ -2606,7 +2624,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>118</v>
       </c>
@@ -2726,7 +2744,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>126</v>
       </c>
@@ -2846,7 +2864,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>134</v>
       </c>
@@ -2966,7 +2984,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>142</v>
       </c>
@@ -3088,7 +3106,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>147</v>
       </c>
@@ -3208,7 +3226,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>158</v>
       </c>
@@ -3332,7 +3350,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>160</v>
       </c>
@@ -3450,7 +3468,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>167</v>
       </c>
@@ -3570,7 +3588,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>174</v>
       </c>
@@ -3692,7 +3710,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>185</v>
       </c>
@@ -3814,7 +3832,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>197</v>
       </c>
@@ -3932,7 +3950,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>199</v>
       </c>
@@ -4052,7 +4070,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>201</v>
       </c>
@@ -4174,7 +4192,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>211</v>
       </c>
@@ -4292,7 +4310,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>213</v>
       </c>
@@ -4412,7 +4430,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>215</v>
       </c>
@@ -4534,7 +4552,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>225</v>
       </c>
@@ -4654,7 +4672,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>233</v>
       </c>
@@ -4774,7 +4792,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>241</v>
       </c>
@@ -4894,7 +4912,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>250</v>
       </c>
@@ -5016,7 +5034,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>260</v>
       </c>
@@ -5138,7 +5156,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>270</v>
       </c>
@@ -5260,7 +5278,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>281</v>
       </c>
@@ -5380,7 +5398,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>290</v>
       </c>
@@ -5498,7 +5516,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>298</v>
       </c>
@@ -5618,7 +5636,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>307</v>
       </c>
@@ -5738,7 +5756,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>319</v>
       </c>
@@ -5858,7 +5876,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>330</v>
       </c>
@@ -5978,7 +5996,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>339</v>
       </c>
@@ -6098,7 +6116,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>349</v>
       </c>
@@ -6216,7 +6234,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>361</v>
       </c>
@@ -6334,7 +6352,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>362</v>
       </c>
@@ -6454,7 +6472,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>363</v>
       </c>
@@ -6576,7 +6594,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>364</v>
       </c>
@@ -6698,7 +6716,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>365</v>
       </c>
@@ -6818,7 +6836,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>375</v>
       </c>
@@ -6938,7 +6956,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>385</v>
       </c>
@@ -7058,7 +7076,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>394</v>
       </c>
@@ -7178,7 +7196,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>403</v>
       </c>
@@ -7298,7 +7316,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>410</v>
       </c>
@@ -7416,7 +7434,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>417</v>
       </c>
@@ -7534,7 +7552,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>423</v>
       </c>
@@ -7652,7 +7670,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>429</v>
       </c>
@@ -7770,7 +7788,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>435</v>
       </c>
@@ -7888,7 +7906,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>436</v>
       </c>
@@ -8008,7 +8026,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>437</v>
       </c>
@@ -8130,7 +8148,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>442</v>
       </c>
@@ -8248,7 +8266,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>449</v>
       </c>
@@ -8366,7 +8384,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>454</v>
       </c>
@@ -8484,7 +8502,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>460</v>
       </c>
@@ -8604,7 +8622,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>466</v>
       </c>
@@ -8722,7 +8740,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>467</v>
       </c>
@@ -8842,7 +8860,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>468</v>
       </c>
@@ -8964,7 +8982,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>469</v>
       </c>
@@ -9082,7 +9100,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>478</v>
       </c>
@@ -9200,7 +9218,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>482</v>
       </c>
@@ -9219,7 +9237,7 @@
         <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>79</v>
@@ -9319,6 +9337,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AP62">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI61">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T10:41:47+00:00</t>
+    <t>2023-04-04T07:17:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T07:17:27+00:00</t>
+    <t>2023-04-04T10:49:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:49:31+00:00</t>
+    <t>2023-04-04T13:39:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T13:39:29+00:00</t>
+    <t>2023-04-17T12:49:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -867,7 +867,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/hiv-cbs/identifier/hiv-diagnosis</t>
+    <t>http://openhie.org/fhir/training-solution-1/identifier/hiv-diagnosis</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>

--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2391" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2393" uniqueCount="489">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:49:16+00:00</t>
+    <t>2023-05-26T13:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -1686,7 +1686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1773,77 +1773,85 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="B21" t="s" s="2">
         <v>36</v>
       </c>
     </row>

--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:09:55+00:00</t>
+    <t>2023-05-26T15:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2393" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2394" uniqueCount="489">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T15:10:57+00:00</t>
+    <t>2023-05-29T05:09:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -492,11 +492,14 @@
     <t>Allows identification of the condition as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:system}
+    <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
-    <t>openAtEnd</t>
+    <t>Slice based on the type of identifier.</t>
+  </si>
+  <si>
+    <t>open</t>
   </si>
   <si>
     <t>Event.identifier</t>
@@ -550,9 +553,6 @@
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -3193,12 +3193,14 @@
       <c r="AB11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AC11" s="2"/>
+      <c r="AC11" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="AD11" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>147</v>
@@ -3216,7 +3218,7 @@
         <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>79</v>
@@ -3225,10 +3227,10 @@
         <v>79</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>79</v>
@@ -3236,13 +3238,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>147</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>79</v>
@@ -3340,7 +3342,7 @@
         <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>79</v>
@@ -3349,10 +3351,10 @@
         <v>79</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>79</v>
@@ -3360,10 +3362,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3386,13 +3388,13 @@
         <v>79</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3443,7 +3445,7 @@
         <v>79</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3467,7 +3469,7 @@
         <v>79</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>79</v>
@@ -3478,10 +3480,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3510,7 +3512,7 @@
         <v>137</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>139</v>
@@ -3551,16 +3553,16 @@
         <v>79</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>173</v>
@@ -3587,7 +3589,7 @@
         <v>79</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>79</v>
@@ -3868,13 +3870,13 @@
         <v>79</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3925,7 +3927,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3949,7 +3951,7 @@
         <v>79</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>79</v>
@@ -3992,7 +3994,7 @@
         <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>139</v>
@@ -4033,16 +4035,16 @@
         <v>79</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>173</v>
@@ -4069,7 +4071,7 @@
         <v>79</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>79</v>
@@ -4228,13 +4230,13 @@
         <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4285,7 +4287,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4309,7 +4311,7 @@
         <v>79</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>79</v>
@@ -4352,7 +4354,7 @@
         <v>137</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>139</v>
@@ -4393,16 +4395,16 @@
         <v>79</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>173</v>
@@ -4429,7 +4431,7 @@
         <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>79</v>
@@ -4588,7 +4590,7 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>227</v>
@@ -4728,7 +4730,7 @@
         <v>79</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>79</v>
@@ -4828,7 +4830,7 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>243</v>
@@ -5070,7 +5072,7 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>262</v>
@@ -5314,7 +5316,7 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>283</v>
@@ -6270,13 +6272,13 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6327,7 +6329,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6351,7 +6353,7 @@
         <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6394,7 +6396,7 @@
         <v>137</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>139</v>
@@ -6435,16 +6437,16 @@
         <v>79</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>173</v>
@@ -6471,7 +6473,7 @@
         <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6630,7 +6632,7 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>262</v>
@@ -7824,13 +7826,13 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7881,7 +7883,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7905,7 +7907,7 @@
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7948,7 +7950,7 @@
         <v>137</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>139</v>
@@ -8025,7 +8027,7 @@
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -8658,13 +8660,13 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8715,7 +8717,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8739,7 +8741,7 @@
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>
@@ -8782,7 +8784,7 @@
         <v>137</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>139</v>
@@ -8859,7 +8861,7 @@
         <v>79</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>79</v>

--- a/branches/master/StructureDefinition-hiv-diagnosis.xlsx
+++ b/branches/master/StructureDefinition-hiv-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:56:41+00:00</t>
+    <t>2023-06-20T13:53:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
